--- a/Documents/_聲韻調對照表.xlsx
+++ b/Documents/_聲韻調對照表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4178A19C-51D6-4011-8904-56A65DC91879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68373CD-0350-4C44-8B69-EBAB6B68804E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{7E808FC4-FD7B-4D2F-8735-FF65DCE8E5C1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{7E808FC4-FD7B-4D2F-8735-FF65DCE8E5C1}"/>
   </bookViews>
   <sheets>
     <sheet name="【聲】聲母對照表" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="872">
   <si>
     <t>識別號</t>
   </si>
@@ -2292,9 +2292,6 @@
     <t>[</t>
   </si>
   <si>
-    <t>a◌</t>
-  </si>
-  <si>
     <t>ㄚ◌</t>
   </si>
   <si>
@@ -2311,9 +2308,6 @@
   </si>
   <si>
     <t>]</t>
-  </si>
-  <si>
-    <t>a̍◌</t>
   </si>
   <si>
     <t>ㄚ◌˙</t>
@@ -2352,19 +2346,10 @@
     <t>U+0301</t>
   </si>
   <si>
-    <t>U+030C</t>
-  </si>
-  <si>
     <t>調號</t>
   </si>
   <si>
     <t>U+030A</t>
-  </si>
-  <si>
-    <t>U+0300</t>
-  </si>
-  <si>
-    <t>U+0302</t>
   </si>
   <si>
     <t>U+030B</t>
@@ -2782,12 +2767,32 @@
     <t>調名</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>ah</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>a̍h</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>U+030D</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Charis</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Noto Sans TC Medium</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="41">
+  <fonts count="42">
     <font>
       <sz val="16"/>
       <color theme="1"/>
@@ -3069,6 +3074,11 @@
       <name val="Noto Sans TC Medium"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Charis"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3158,7 +3168,7 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3306,20 +3316,11 @@
     <xf numFmtId="0" fontId="36" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -3328,6 +3329,9 @@
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7959,7 +7963,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C343D1B8-C933-4F87-997F-1644EE992569}">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="25.5"/>
   <cols>
     <col min="1" max="1" width="7.58203125" customWidth="1"/>
@@ -7967,7 +7971,7 @@
     <col min="9" max="14" width="12.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7978,7 +7982,7 @@
         <v>697</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>695</v>
@@ -7990,28 +7994,28 @@
         <v>701</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>757</v>
-      </c>
       <c r="J1" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>760</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>700</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:16">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -8053,7 +8057,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:16">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -8085,7 +8089,7 @@
         <v>713</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>714</v>
@@ -8097,7 +8101,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:16">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -8139,7 +8143,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:16">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -8171,7 +8175,7 @@
         <v>729</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>730</v>
@@ -8183,7 +8187,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:16">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -8225,7 +8229,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:16">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -8254,11 +8258,11 @@
         <v>742</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>745</v>
+        <v>867</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>707</v>
@@ -8267,18 +8271,18 @@
         <v>744</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:16">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>747</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>748</v>
       </c>
       <c r="E8" s="1">
         <v>121</v>
@@ -8293,57 +8297,68 @@
         <v>8</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>752</v>
+        <v>868</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="G11" s="56" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="J10" s="20" t="s">
         <v>871</v>
       </c>
-      <c r="H11" s="56" t="s">
-        <v>764</v>
-      </c>
-      <c r="I11" s="56" t="s">
-        <v>868</v>
-      </c>
-      <c r="J11" s="56" t="s">
-        <v>854</v>
-      </c>
-      <c r="K11" s="56" t="s">
-        <v>869</v>
-      </c>
-      <c r="L11" s="56" t="s">
+      <c r="P10" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="G11" s="53" t="s">
+        <v>866</v>
+      </c>
+      <c r="H11" s="53" t="s">
+        <v>761</v>
+      </c>
+      <c r="I11" s="53" t="s">
+        <v>863</v>
+      </c>
+      <c r="J11" s="53" t="s">
+        <v>849</v>
+      </c>
+      <c r="K11" s="53" t="s">
+        <v>864</v>
+      </c>
+      <c r="L11" s="53" t="s">
+        <v>850</v>
+      </c>
+      <c r="M11" s="53" t="s">
+        <v>865</v>
+      </c>
+      <c r="N11" s="53" t="s">
+        <v>851</v>
+      </c>
+      <c r="P11" s="53" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="36.75">
+      <c r="G12" s="14" t="s">
         <v>855</v>
-      </c>
-      <c r="M11" s="56" t="s">
-        <v>870</v>
-      </c>
-      <c r="N11" s="56" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="G12" s="14" t="s">
-        <v>860</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
       </c>
       <c r="I12" s="1"/>
-      <c r="J12" s="49" t="str">
+      <c r="J12" s="14" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a"), "")</f>
         <v>a</v>
       </c>
@@ -8353,81 +8368,93 @@
         <v>ㄚ</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="N12" s="50" t="str">
+        <v>759</v>
+      </c>
+      <c r="N12" s="49" t="str">
         <f t="shared" ref="N12:N14" si="0" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(M12,4)))), "")</f>
         <v>ā</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="P12" s="54" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a"), "")</f>
+        <v>a</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="36.75">
       <c r="G13" s="14" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="H13" s="1">
         <v>2</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="J13" s="49" t="str">
-        <f t="shared" ref="J13:J20" si="1" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(I13,4)))), "")</f>
+        <v>760</v>
+      </c>
+      <c r="J13" s="14" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT($I13,4)))), "")</f>
         <v>á</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="L13" s="1" t="str">
-        <f t="shared" ref="L13:L18" si="2" xml:space="preserve"> IFERROR( _xlfn.CONCAT("ㄚ", _xlfn.UNICHAR(HEX2DEC(RIGHT(K13,4)))), "")</f>
+        <f t="shared" ref="L13:L18" si="1" xml:space="preserve"> IFERROR( _xlfn.CONCAT("ㄚ", _xlfn.UNICHAR(HEX2DEC(RIGHT(K13,4)))), "")</f>
         <v>ㄚ̀</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="N13" s="50" t="str">
+        <v>853</v>
+      </c>
+      <c r="N13" s="49" t="str">
         <f t="shared" si="0"/>
         <v>ǎ</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="P13" s="54" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT($I13,4)))), "")</f>
+        <v>á</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="36.75">
       <c r="G14" s="14" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H14" s="1">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="J14" s="49" t="str">
+        <v>845</v>
+      </c>
+      <c r="J14" s="14" t="str">
+        <f t="shared" ref="J14:J21" si="2" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT($I14,4)))), "")</f>
+        <v>à</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="L14" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>ǎ</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="L14" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>ㄚ˪</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="N14" s="50" t="str">
+        <v>845</v>
+      </c>
+      <c r="N14" s="49" t="str">
         <f t="shared" si="0"/>
         <v>à</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="P14" s="54" t="str">
+        <f t="shared" ref="P14:P21" si="3" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT($I14,4)))), "")</f>
+        <v>à</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="36.75">
       <c r="G15" s="14" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="H15" s="1">
         <v>4</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="49" t="str">
-        <f t="shared" si="1"/>
+      <c r="J15" s="14" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K15" s="1"/>
@@ -8436,164 +8463,188 @@
         <v>ㄚㆷ</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="N15" s="51" t="str">
+        <v>862</v>
+      </c>
+      <c r="N15" s="49" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(M15,4))), "h"), "")</f>
         <v>āh</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="P15" s="54" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="36.75">
       <c r="G16" s="14" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="H16" s="1">
         <v>5</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="J16" s="49" t="str">
+        <v>853</v>
+      </c>
+      <c r="J16" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>ǎ</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="L16" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>à</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>852</v>
-      </c>
-      <c r="L16" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>ㄚ́</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>852</v>
-      </c>
-      <c r="N16" s="50" t="str">
-        <f t="shared" ref="N16:N17" si="3" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(M16,4)))), "")</f>
+        <v>847</v>
+      </c>
+      <c r="N16" s="49" t="str">
+        <f t="shared" ref="N16:N17" si="4" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(M16,4)))), "")</f>
         <v>á</v>
       </c>
-    </row>
-    <row r="17" spans="7:14">
-      <c r="G17" s="14" t="s">
-        <v>861</v>
-      </c>
-      <c r="H17" s="52">
-        <v>6</v>
-      </c>
-      <c r="I17" s="52" t="s">
-        <v>767</v>
-      </c>
-      <c r="J17" s="53" t="str">
-        <f t="shared" si="1"/>
-        <v>â</v>
-      </c>
-      <c r="K17" s="54" t="s">
-        <v>850</v>
-      </c>
-      <c r="L17" s="54" t="str">
-        <f t="shared" si="2"/>
-        <v>ㄚ̀</v>
-      </c>
-      <c r="M17" s="54" t="s">
-        <v>858</v>
-      </c>
-      <c r="N17" s="55" t="str">
+      <c r="P16" s="54" t="str">
         <f t="shared" si="3"/>
         <v>ǎ</v>
       </c>
     </row>
-    <row r="18" spans="7:14">
+    <row r="17" spans="7:16" ht="36.75">
+      <c r="G17" s="14" t="s">
+        <v>856</v>
+      </c>
+      <c r="H17" s="50">
+        <v>6</v>
+      </c>
+      <c r="I17" s="50" t="s">
+        <v>847</v>
+      </c>
+      <c r="J17" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>á</v>
+      </c>
+      <c r="K17" s="51" t="s">
+        <v>845</v>
+      </c>
+      <c r="L17" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄚ̀</v>
+      </c>
+      <c r="M17" s="51" t="s">
+        <v>853</v>
+      </c>
+      <c r="N17" s="52" t="str">
+        <f t="shared" si="4"/>
+        <v>ǎ</v>
+      </c>
+      <c r="P17" s="54" t="str">
+        <f t="shared" si="3"/>
+        <v>á</v>
+      </c>
+    </row>
+    <row r="18" spans="7:16" ht="36.75">
       <c r="G18" s="14" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="H18" s="1">
         <v>7</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="J18" s="49" t="str">
+        <v>759</v>
+      </c>
+      <c r="J18" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>ā</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="L18" s="1" t="str">
         <f t="shared" si="1"/>
+        <v>ㄚ˫</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="N18" s="49" t="str">
+        <f t="shared" ref="N18" si="5" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(M18,4)))), "")</f>
+        <v>â</v>
+      </c>
+      <c r="P18" s="54" t="str">
+        <f t="shared" si="3"/>
         <v>ā</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="L18" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>ㄚ˫</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="N18" s="50" t="str">
-        <f t="shared" ref="N18" si="4" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(M18,4)))), "")</f>
-        <v>â</v>
-      </c>
-    </row>
-    <row r="19" spans="7:14">
+    </row>
+    <row r="19" spans="7:16" ht="36.75">
       <c r="G19" s="14" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="H19" s="1">
         <v>8</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="J19" s="49" t="str">
-        <f t="shared" si="1"/>
-        <v>á</v>
+        <v>869</v>
+      </c>
+      <c r="J19" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>a̍</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="L19" s="1" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("ㄚ", "ㆷ", _xlfn.UNICHAR(HEX2DEC(RIGHT(K19,4)))), "")</f>
         <v>ㄚㆷ˙</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>852</v>
-      </c>
-      <c r="N19" s="51" t="str">
+        <v>847</v>
+      </c>
+      <c r="N19" s="49" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(M19,4))), "h"), "")</f>
         <v>áh</v>
       </c>
-    </row>
-    <row r="20" spans="7:14">
+      <c r="P19" s="54" t="str">
+        <f t="shared" si="3"/>
+        <v>a̍</v>
+      </c>
+    </row>
+    <row r="20" spans="7:16" ht="36.75">
       <c r="G20" s="14" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="H20" s="1">
         <v>9</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="J20" s="49" t="str">
-        <f t="shared" si="1"/>
+        <v>763</v>
+      </c>
+      <c r="J20" s="14" t="str">
+        <f t="shared" si="2"/>
         <v>a̋</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
-    </row>
-    <row r="21" spans="7:14">
+      <c r="P20" s="54" t="str">
+        <f t="shared" si="3"/>
+        <v>a̋</v>
+      </c>
+    </row>
+    <row r="21" spans="7:16" ht="36.75">
       <c r="G21" s="14" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="J21" s="49" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(I21,4)))), "")</f>
+        <v>762</v>
+      </c>
+      <c r="J21" s="14" t="str">
+        <f t="shared" si="2"/>
         <v>å</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="L21" s="1" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("ㄚ", _xlfn.UNICHAR(HEX2DEC(RIGHT(K21,4)))), "")</f>
@@ -8601,6 +8652,10 @@
       </c>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
+      <c r="P21" s="54" t="str">
+        <f t="shared" si="3"/>
+        <v>å</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -8621,58 +8676,58 @@
     <row r="1" spans="2:19" ht="9" customHeight="1"/>
     <row r="2" spans="2:19">
       <c r="B2" s="21" t="s">
+        <v>764</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>765</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>766</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>767</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>768</v>
+      </c>
+      <c r="G2" s="21" t="s">
         <v>769</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="H2" s="23" t="s">
         <v>770</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="I2" s="21" t="s">
         <v>771</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="J2" s="21" t="s">
         <v>772</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="K2" s="21" t="s">
         <v>773</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="L2" s="23" t="s">
         <v>774</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="M2" s="24" t="s">
         <v>775</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="N2" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="O2" s="21" t="s">
         <v>777</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="P2" s="21" t="s">
         <v>778</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="Q2" s="21" t="s">
         <v>779</v>
-      </c>
-      <c r="M2" s="24" t="s">
-        <v>780</v>
-      </c>
-      <c r="N2" s="22" t="s">
-        <v>781</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>782</v>
-      </c>
-      <c r="P2" s="21" t="s">
-        <v>783</v>
-      </c>
-      <c r="Q2" s="21" t="s">
-        <v>784</v>
       </c>
       <c r="R2" s="21" t="s">
         <v>4</v>
       </c>
       <c r="S2" s="21" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="57.75">
@@ -8683,22 +8738,22 @@
         <v>9</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="F3" s="27">
         <v>20</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="J3" s="31" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(I3,4)))), "")</f>
@@ -8720,7 +8775,7 @@
         <v>ah7</v>
       </c>
       <c r="O3" s="35" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="P3" s="36" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("ㄚ", "ㆷ", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+02D9",4))))</f>
@@ -8730,10 +8785,10 @@
         <v>50</v>
       </c>
       <c r="R3" s="35" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="S3" s="35" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="57.75">
@@ -8747,26 +8802,26 @@
         <v>702</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="F4" s="27">
         <v>44</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="J4" s="31" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(I4,4)))), "")</f>
         <v>ā</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="L4" s="33" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("dong", B4)</f>
@@ -8786,13 +8841,13 @@
         <v>ㄚ</v>
       </c>
       <c r="Q4" s="35" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="R4" s="35" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="S4" s="35" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="57.75">
@@ -8806,26 +8861,26 @@
         <v>732</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="F5" s="39">
         <v>13</v>
       </c>
       <c r="G5" s="40" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="H5" s="41" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="I5" s="42" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="J5" s="43" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(I5,4)))), "")</f>
         <v>á</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="L5" s="45" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("dong", B5)</f>
@@ -8840,20 +8895,20 @@
         <v>dong/</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="P5" s="48" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("ㄚ ",_xlfn.UNICHAR(HEX2DEC(RIGHT(O5,4))))</f>
         <v>ㄚ ́</v>
       </c>
       <c r="Q5" s="47" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="R5" s="47" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="S5" s="47" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
     </row>
     <row r="6" spans="2:19" ht="57.75">
@@ -8864,29 +8919,29 @@
         <v>4</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="F6" s="27">
         <v>53</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="J6" s="31" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(I6,4)))), "")</f>
         <v>ǎ</v>
       </c>
       <c r="K6" s="32" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="L6" s="33" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("dong", B6)</f>
@@ -8901,7 +8956,7 @@
         <v>dong\</v>
       </c>
       <c r="O6" s="35" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="P6" s="36" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("ㄚ ",_xlfn.UNICHAR(HEX2DEC(RIGHT(O6,4))))</f>
@@ -8911,10 +8966,10 @@
         <v>32</v>
       </c>
       <c r="R6" s="35" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="S6" s="35" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
     </row>
     <row r="7" spans="2:19" ht="57.75">
@@ -8925,7 +8980,7 @@
         <v>99</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="E7" s="38"/>
       <c r="F7" s="39"/>
@@ -8959,26 +9014,26 @@
         <v>716</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="F8" s="27">
         <v>21</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="H8" s="29" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="J8" s="31" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(I8,4)))), "")</f>
         <v>à</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="L8" s="33" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("dong", B8)</f>
@@ -8993,7 +9048,7 @@
         <v>dong_</v>
       </c>
       <c r="O8" s="35" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="P8" s="36" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("ㄚ",_xlfn.UNICHAR(HEX2DEC(RIGHT(O8,4))))</f>
@@ -9003,10 +9058,10 @@
         <v>26</v>
       </c>
       <c r="R8" s="35" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="S8" s="35" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
     </row>
     <row r="9" spans="2:19" ht="57.75">
@@ -9020,26 +9075,26 @@
         <v>708</v>
       </c>
       <c r="E9" s="38" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="F9" s="39">
         <v>22</v>
       </c>
       <c r="G9" s="40" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="H9" s="41" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="I9" s="42" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="J9" s="43" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(I9,4)))), "")</f>
         <v>â</v>
       </c>
       <c r="K9" s="44" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="L9" s="45" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("dong", B9)</f>
@@ -9054,20 +9109,20 @@
         <v>dong-</v>
       </c>
       <c r="O9" s="47" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="P9" s="48" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("ㄚ",_xlfn.UNICHAR(HEX2DEC(RIGHT(O9,4))))</f>
         <v>ㄚ˫</v>
       </c>
       <c r="Q9" s="47" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="R9" s="47" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="S9" s="47" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="57.75">
@@ -9081,26 +9136,26 @@
         <v>740</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="F10" s="27">
         <v>32</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="J10" s="31" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(I10,4))), "h"), "")</f>
         <v>āh</v>
       </c>
       <c r="K10" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="L10" s="33" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("dok", B10)</f>
@@ -9123,10 +9178,10 @@
         <v>744</v>
       </c>
       <c r="R10" s="35" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="S10" s="35" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
     </row>
     <row r="11" spans="2:19" ht="57.75">
@@ -9137,29 +9192,29 @@
         <v>8</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="F11" s="39">
         <v>121</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="H11" s="41" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="I11" s="42" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="J11" s="43" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(I11,4))), "h"), "")</f>
         <v>áh</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="L11" s="45" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("dok", B11)</f>
@@ -9174,20 +9229,20 @@
         <v>dok]</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="P11" s="48" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("ㄚ", "ㆷ", _xlfn.UNICHAR(HEX2DEC(RIGHT(O11,4))))</f>
         <v>ㄚㆷ˙</v>
       </c>
       <c r="Q11" s="47" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="R11" s="47" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="S11" s="47" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
     </row>
   </sheetData>
